--- a/proposed_data_structure.xlsx
+++ b/proposed_data_structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gfay/research/hydra_sim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{708B9D53-3264-2A43-BECE-1A00DA1728F4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942969BA-BAE7-5940-8BF3-4593AF0C1F26}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="48020" yWindow="-5540" windowWidth="19180" windowHeight="14640" activeTab="4" xr2:uid="{975A5D88-3673-E240-BD78-CAFAE9BB8352}"/>
   </bookViews>
